--- a/Task2_交付物/Task1/evidence_battery_EV_screened_v0.9.xlsx
+++ b/Task2_交付物/Task1/evidence_battery_EV_screened_v0.9.xlsx
@@ -1829,7 +1829,7 @@
       </c>
       <c r="N6" s="14" t="inlineStr">
         <is>
-          <t>◆随产业</t>
+          <t>电池材料</t>
         </is>
       </c>
       <c r="O6" s="14" t="inlineStr">
@@ -4048,7 +4048,7 @@
       </c>
       <c r="N27" s="14" t="inlineStr">
         <is>
-          <t>◆电子/光电</t>
+          <t>动力电池</t>
         </is>
       </c>
       <c r="O27" s="14" t="inlineStr">
@@ -8772,7 +8772,7 @@
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>General_Manufacturing</t>
+          <t>EV_Battery</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>General_Manufacturing</t>
+          <t>EV_Battery</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>General_Manufacturing</t>
+          <t>EV_Battery</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
@@ -8958,7 +8958,7 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>General_Manufacturing</t>
+          <t>EV_Battery</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>General_Manufacturing</t>
+          <t>EV_Battery</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
@@ -9144,7 +9144,7 @@
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>General_Manufacturing</t>
+          <t>EV_Battery</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>General_Manufacturing</t>
+          <t>Energy_Storage</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
@@ -9268,7 +9268,7 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>General_Manufacturing</t>
+          <t>EV_Battery</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -9330,7 +9330,7 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>General_Manufacturing</t>
+          <t>EV_Battery</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -9392,7 +9392,7 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>General_Manufacturing</t>
+          <t>EV_Battery</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -9454,7 +9454,7 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>General_Manufacturing</t>
+          <t>EV_Battery</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>General_Manufacturing</t>
+          <t>EV_Battery</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -9578,7 +9578,7 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>General_Manufacturing</t>
+          <t>EV_Battery</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
@@ -9640,7 +9640,7 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>General_Manufacturing</t>
+          <t>EV_Battery</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
@@ -9764,7 +9764,7 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>General_Manufacturing</t>
+          <t>Energy_Storage</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>General_Manufacturing</t>
+          <t>Energy_Storage</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -9888,7 +9888,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>General_Manufacturing</t>
+          <t>Electronics_Manufacturing</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -9950,7 +9950,7 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>General_Manufacturing</t>
+          <t>Electronics_Manufacturing</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>General_Manufacturing</t>
+          <t>Electronics_Manufacturing</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
@@ -10074,7 +10074,7 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>General_Manufacturing</t>
+          <t>Electronics_Manufacturing</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
@@ -10136,7 +10136,7 @@
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>General_Manufacturing</t>
+          <t>Electronics_Manufacturing</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
@@ -10198,7 +10198,7 @@
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>General_Manufacturing</t>
+          <t>EV_Battery</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
@@ -10260,7 +10260,7 @@
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>General_Manufacturing</t>
+          <t>EV_Battery</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
@@ -10384,7 +10384,7 @@
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>General_Manufacturing</t>
+          <t>Energy_Storage</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
@@ -10446,7 +10446,7 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>General_Manufacturing</t>
+          <t>Electronics_Manufacturing</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>General_Manufacturing</t>
+          <t>EV_Battery</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
@@ -10570,7 +10570,7 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>General_Manufacturing</t>
+          <t>EV_Battery</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
@@ -10632,7 +10632,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>General_Manufacturing</t>
+          <t>EV_Battery</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -10694,7 +10694,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>General_Manufacturing</t>
+          <t>EV_Battery</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -10756,7 +10756,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>General_Manufacturing</t>
+          <t>EV_Battery</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -10818,7 +10818,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>General_Manufacturing</t>
+          <t>EV_Battery</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -10880,7 +10880,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>General_Manufacturing</t>
+          <t>EV_Battery</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -10942,7 +10942,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>General_Manufacturing</t>
+          <t>EV_Battery</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -11314,7 +11314,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>General_Manufacturing</t>
+          <t>EV_Battery</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -11376,7 +11376,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>General_Manufacturing</t>
+          <t>EV_Battery</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -11438,7 +11438,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>General_Manufacturing</t>
+          <t>EV_Battery</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -11500,7 +11500,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>General_Manufacturing</t>
+          <t>EV_Battery</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -11562,7 +11562,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>General_Manufacturing</t>
+          <t>EV_Battery</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -11624,7 +11624,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>General_Manufacturing</t>
+          <t>EV_Battery</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -11686,7 +11686,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>General_Manufacturing</t>
+          <t>EV_Battery</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -11805,7 +11805,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -11946,6 +11946,18 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>v0.9 industry correction</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>task1_annotations.industry 全 49 行改为按 sources.related_industries 派生（与 evidence_metadata 派生值、即 Task 4 元数据过滤口径一致）；此前 27/30 行为占位值 General_Manufacturing。同时修正 2 条与证据内容不符的 related_industries 标签：TRD_001 ◆电子/光电→动力电池（数据实为 HS 870380 整车 + 850760 锂电池）、MOFCOM_002 ◆随产业→电池材料</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Task2_交付物/Task1/evidence_battery_EV_screened_v0.9.xlsx
+++ b/Task2_交付物/Task1/evidence_battery_EV_screened_v0.9.xlsx
@@ -631,7 +631,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -684,6 +684,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1204,7 +1205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y50"/>
+  <dimension ref="A1:AA50"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="16.8"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="25"/>
@@ -1336,6 +1337,16 @@
           <t>screening_note</t>
         </is>
       </c>
+      <c r="Z1" s="18" t="inlineStr">
+        <is>
+          <t>date_precision</t>
+        </is>
+      </c>
+      <c r="AA1" s="18" t="inlineStr">
+        <is>
+          <t>shared_source_group</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="46" customHeight="1">
       <c r="A2" s="14" t="inlineStr">
@@ -1443,6 +1454,11 @@
           <t>与EV/battery供应链、关键材料、出口管制或相关工业政策高度相关</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="46" customHeight="1">
       <c r="A3" s="14" t="inlineStr">
@@ -1550,6 +1566,11 @@
           <t>与EV/battery供应链、关键材料、出口管制或相关工业政策高度相关</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="31" customHeight="1">
       <c r="A4" s="14" t="inlineStr">
@@ -1657,6 +1678,11 @@
           <t>可能影响产业环境，但需人工确认与EV/battery关联程度</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="31" customHeight="1">
       <c r="A5" s="14" t="inlineStr">
@@ -1764,6 +1790,11 @@
           <t>与EV/battery供应链、关键材料、出口管制或相关工业政策高度相关</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="31" customHeight="1">
       <c r="A6" s="14" t="inlineStr">
@@ -1871,6 +1902,11 @@
           <t>与EV/battery供应链、关键材料、出口管制或相关工业政策高度相关</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="46" customHeight="1">
       <c r="A7" s="14" t="inlineStr">
@@ -1978,6 +2014,11 @@
           <t>可能影响产业环境，但需人工确认与EV/battery关联程度</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="61" customHeight="1">
       <c r="A8" s="14" t="inlineStr">
@@ -2085,6 +2126,11 @@
           <t>可能影响产业环境，但需人工确认与EV/battery关联程度</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="61" customHeight="1">
       <c r="A9" s="14" t="inlineStr">
@@ -2192,6 +2238,11 @@
           <t>可能影响产业环境，但需人工确认与EV/battery关联程度</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="51" customHeight="1">
       <c r="A10" s="14" t="inlineStr">
@@ -2295,6 +2346,11 @@
           <t>可能影响产业环境，但需人工确认与EV/battery关联程度</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="31" customHeight="1">
       <c r="A11" s="14" t="inlineStr">
@@ -2398,6 +2454,11 @@
           <t>可能影响产业环境，但需人工确认与EV/battery关联程度</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="31" customHeight="1">
       <c r="A12" s="14" t="inlineStr">
@@ -2501,6 +2562,11 @@
           <t>可能影响产业环境，但需人工确认与EV/battery关联程度</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="31" customHeight="1">
       <c r="A13" s="14" t="inlineStr">
@@ -2608,6 +2674,11 @@
           <t>可能影响产业环境，但需人工确认与EV/battery关联程度</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="31" customHeight="1">
       <c r="A14" s="14" t="inlineStr">
@@ -2711,6 +2782,11 @@
           <t>可能影响产业环境，但需人工确认与EV/battery关联程度</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="31" customHeight="1">
       <c r="A15" s="14" t="inlineStr">
@@ -2745,7 +2821,7 @@
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="H15" s="14" t="n"/>
@@ -2818,6 +2894,11 @@
           <t>可能影响产业环境，但需人工确认与EV/battery关联程度</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="31" customHeight="1">
       <c r="A16" s="14" t="inlineStr">
@@ -2921,6 +3002,11 @@
           <t>可能影响产业环境，但需人工确认与EV/battery关联程度</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="46" customHeight="1">
       <c r="A17" s="14" t="inlineStr">
@@ -3028,6 +3114,11 @@
           <t>可能影响产业环境，但需人工确认与EV/battery关联程度</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="31" customHeight="1">
       <c r="A18" s="14" t="inlineStr">
@@ -3131,6 +3222,11 @@
           <t>可能影响产业环境，但需人工确认与EV/battery关联程度</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="46" customHeight="1">
       <c r="A19" s="14" t="inlineStr">
@@ -3234,6 +3330,11 @@
           <t>可能影响产业环境，但需人工确认与EV/battery关联程度</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="51" customHeight="1">
       <c r="A20" s="14" t="inlineStr">
@@ -3325,7 +3426,11 @@
         </is>
       </c>
       <c r="U20" s="14" t="n"/>
-      <c r="V20" s="14" t="n"/>
+      <c r="V20" s="14" t="inlineStr">
+        <is>
+          <t>与 CASE_005/CASE_006 同源（同一篇国盛证券研报，经腾讯新闻转载）；三家公司的年报原文仍待补。</t>
+        </is>
+      </c>
       <c r="W20" s="14" t="inlineStr">
         <is>
           <t>MEDIUM</t>
@@ -3339,6 +3444,16 @@
       <c r="Y20" s="14" t="inlineStr">
         <is>
           <t>可能影响产业环境，但需人工确认与EV/battery关联程度</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>GS_OPTICAL_20251130</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3547,11 @@
         </is>
       </c>
       <c r="U21" s="14" t="n"/>
-      <c r="V21" s="14" t="n"/>
+      <c r="V21" s="14" t="inlineStr">
+        <is>
+          <t>与 CASE_004/CASE_006 同源（同一篇国盛证券研报，经腾讯新闻转载）；年报原文仍待补。</t>
+        </is>
+      </c>
       <c r="W21" s="14" t="inlineStr">
         <is>
           <t>MEDIUM</t>
@@ -3446,6 +3565,16 @@
       <c r="Y21" s="14" t="inlineStr">
         <is>
           <t>可能影响产业环境，但需人工确认与EV/battery关联程度</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>GS_OPTICAL_20251130</t>
         </is>
       </c>
     </row>
@@ -3539,7 +3668,11 @@
         </is>
       </c>
       <c r="U22" s="14" t="n"/>
-      <c r="V22" s="14" t="n"/>
+      <c r="V22" s="14" t="inlineStr">
+        <is>
+          <t>与 CASE_004/CASE_005 同源（同一篇国盛证券研报，经腾讯新闻转载）；年报原文仍待补。</t>
+        </is>
+      </c>
       <c r="W22" s="14" t="inlineStr">
         <is>
           <t>MEDIUM</t>
@@ -3553,6 +3686,16 @@
       <c r="Y22" s="14" t="inlineStr">
         <is>
           <t>可能影响产业环境，但需人工确认与EV/battery关联程度</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>GS_OPTICAL_20251130</t>
         </is>
       </c>
     </row>
@@ -3662,6 +3805,11 @@
           <t>可能影响产业环境，但需人工确认与EV/battery关联程度</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="31" customHeight="1">
       <c r="A24" s="14" t="inlineStr">
@@ -3769,6 +3917,11 @@
           <t>可能影响产业环境，但需人工确认与EV/battery关联程度</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="46" customHeight="1">
       <c r="A25" s="14" t="inlineStr">
@@ -3814,7 +3967,7 @@
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
-          <t>https://www.federalregister.gov/documents/2025/11/12/2025-19846/one-year-suspension-of-expansion-of-end-user-controls-for-affiliates-of-certain-listed-entities</t>
+          <t>https://www.federalregister.gov/documents/search?conditions%5Bterm%5D=end-user+controls+affiliates&amp;conditions%5Btype%5D%5B%5D=RULE</t>
         </is>
       </c>
       <c r="K25" s="14" t="inlineStr">
@@ -3860,7 +4013,11 @@
         </is>
       </c>
       <c r="U25" s="14" t="n"/>
-      <c r="V25" s="14" t="n"/>
+      <c r="V25" s="14" t="inlineStr">
+        <is>
+          <t>时间线型案例，由 BIS_001（2025-09-30 规则）与 BIS_002（2025-11-12 暂停）组成，故来源指向联邦公报的规则族检索而非单篇。</t>
+        </is>
+      </c>
       <c r="W25" s="14" t="inlineStr">
         <is>
           <t>HIGH</t>
@@ -3874,6 +4031,11 @@
       <c r="Y25" s="14" t="inlineStr">
         <is>
           <t>与EV/battery供应链、关键材料、出口管制或相关工业政策高度相关</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>day</t>
         </is>
       </c>
     </row>
@@ -3983,6 +4145,11 @@
           <t>可能影响产业环境，但需人工确认与EV/battery关联程度</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="31" customHeight="1">
       <c r="A27" s="14" t="inlineStr">
@@ -4017,7 +4184,7 @@
       </c>
       <c r="G27" s="14" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H27" s="14" t="n"/>
@@ -4028,7 +4195,7 @@
       </c>
       <c r="J27" s="17" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://comtradeplus.un.org/TradeFlow?Frequency=A&amp;Flows=X&amp;CommodityCodes=850760,870380&amp;Partners=842&amp;Reporters=156,458,764,704&amp;period=2018,2019,2020,2021,2022,2023,2024,2025&amp;partner2=0&amp;output=default&amp;AggregateBy=none&amp;BreakdownMode=plus</t>
         </is>
       </c>
       <c r="K27" s="14" t="inlineStr">
@@ -4056,7 +4223,11 @@
           <t>待拉取</t>
         </is>
       </c>
-      <c r="P27" s="14" t="n"/>
+      <c r="P27" s="14" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
       <c r="Q27" s="14" t="inlineStr">
         <is>
           <t>data/raw/trade/TRD_001.csv</t>
@@ -4074,7 +4245,11 @@
         </is>
       </c>
       <c r="U27" s="14" t="n"/>
-      <c r="V27" s="14" t="n"/>
+      <c r="V27" s="14" t="inlineStr">
+        <is>
+          <t>UN Comtrade 快照（CSV 未内嵌下载时间戳，按同批 TRD_002/003 的 2026-09-24 记）；持续更新源。</t>
+        </is>
+      </c>
       <c r="W27" s="14" t="inlineStr">
         <is>
           <t>MEDIUM</t>
@@ -4088,6 +4263,11 @@
       <c r="Y27" s="14" t="inlineStr">
         <is>
           <t>可能影响产业环境，但需人工确认与EV/battery关联程度</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>snapshot</t>
         </is>
       </c>
     </row>
@@ -4124,7 +4304,7 @@
       </c>
       <c r="G28" s="14" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H28" s="14" t="n"/>
@@ -4135,7 +4315,7 @@
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://comtradeplus.un.org/TradeFlow?Frequency=A&amp;Flows=X&amp;CommodityCodes=854140&amp;Partners=842&amp;Reporters=156,458,764,704&amp;period=2018,2019,2020,2021&amp;partner2=0&amp;output=default&amp;AggregateBy=none&amp;BreakdownMode=plus</t>
         </is>
       </c>
       <c r="K28" s="14" t="inlineStr">
@@ -4163,7 +4343,11 @@
           <t>待拉取</t>
         </is>
       </c>
-      <c r="P28" s="14" t="n"/>
+      <c r="P28" s="14" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
       <c r="Q28" s="14" t="inlineStr">
         <is>
           <t>data/raw/trade/TRD_002.xlsx</t>
@@ -4181,7 +4365,11 @@
         </is>
       </c>
       <c r="U28" s="14" t="n"/>
-      <c r="V28" s="14" t="n"/>
+      <c r="V28" s="14" t="inlineStr">
+        <is>
+          <t>UN Comtrade 快照，日期取自下载文件名内嵌时间戳 TradeData_9_24_2026_21_2_36；持续更新源。</t>
+        </is>
+      </c>
       <c r="W28" s="14" t="inlineStr">
         <is>
           <t>MEDIUM</t>
@@ -4195,6 +4383,11 @@
       <c r="Y28" s="14" t="inlineStr">
         <is>
           <t>可能影响产业环境，但需人工确认与EV/battery关联程度</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>snapshot</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4424,7 @@
       </c>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H29" s="14" t="n"/>
@@ -4242,7 +4435,7 @@
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
-          <t>https://comtradeplus.un.org</t>
+          <t>https://comtradeplus.un.org/TradeFlow?Frequency=A&amp;Flows=X&amp;CommodityCodes=8541,8542&amp;Partners=842&amp;Reporters=156,458,764,704&amp;period=2018,2019,2020,2021,2022,2023,2024,2025&amp;partner2=0&amp;output=default&amp;AggregateBy=none&amp;BreakdownMode=plus</t>
         </is>
       </c>
       <c r="K29" s="14" t="inlineStr">
@@ -4270,7 +4463,11 @@
           <t>待拉取</t>
         </is>
       </c>
-      <c r="P29" s="14" t="n"/>
+      <c r="P29" s="14" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
       <c r="Q29" s="14" t="inlineStr">
         <is>
           <t>data/raw/trade/TRD_003.xlsx</t>
@@ -4288,7 +4485,11 @@
         </is>
       </c>
       <c r="U29" s="14" t="n"/>
-      <c r="V29" s="14" t="n"/>
+      <c r="V29" s="14" t="inlineStr">
+        <is>
+          <t>UN Comtrade 快照，日期取自下载文件名内嵌时间戳 TradeData_9_24_2026_21_5_5；持续更新源。</t>
+        </is>
+      </c>
       <c r="W29" s="14" t="inlineStr">
         <is>
           <t>MEDIUM</t>
@@ -4302,6 +4503,11 @@
       <c r="Y29" s="14" t="inlineStr">
         <is>
           <t>可能影响产业环境，但需人工确认与EV/battery关联程度</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>snapshot</t>
         </is>
       </c>
     </row>
@@ -4338,7 +4544,7 @@
       </c>
       <c r="G30" s="14" t="inlineStr">
         <is>
-          <t>持续更新（每日）</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="H30" s="14" t="n"/>
@@ -4377,7 +4583,11 @@
           <t>已核实</t>
         </is>
       </c>
-      <c r="P30" s="14" t="n"/>
+      <c r="P30" s="14" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
       <c r="Q30" s="14" t="inlineStr">
         <is>
           <t>data/raw/database/ITA_001.json.gz</t>
@@ -4395,7 +4605,11 @@
         </is>
       </c>
       <c r="U30" s="14" t="n"/>
-      <c r="V30" s="14" t="n"/>
+      <c r="V30" s="14" t="inlineStr">
+        <is>
+          <t>美国合并筛查清单 API 的本地快照（2026-09-27 抓取）；接口持续更新，非发布日。</t>
+        </is>
+      </c>
       <c r="W30" s="14" t="inlineStr">
         <is>
           <t>HIGH</t>
@@ -4409,6 +4623,11 @@
       <c r="Y30" s="14" t="inlineStr">
         <is>
           <t>与EV/battery供应链、关键材料、出口管制或相关工业政策高度相关</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>snapshot</t>
         </is>
       </c>
     </row>
@@ -4445,7 +4664,7 @@
       </c>
       <c r="G31" s="14" t="inlineStr">
         <is>
-          <t>持续更新（每日）</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="H31" s="14" t="n"/>
@@ -4484,7 +4703,11 @@
           <t>待验证接口</t>
         </is>
       </c>
-      <c r="P31" s="14" t="n"/>
+      <c r="P31" s="14" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
       <c r="Q31" s="14" t="inlineStr">
         <is>
           <t>data/raw/database/FR_001.json.gz</t>
@@ -4502,7 +4725,11 @@
         </is>
       </c>
       <c r="U31" s="14" t="n"/>
-      <c r="V31" s="14" t="n"/>
+      <c r="V31" s="14" t="inlineStr">
+        <is>
+          <t>美国联邦公报 API 的本地快照（2026-09-27 抓取，检索词 301 tariff）；接口持续更新，非发布日。</t>
+        </is>
+      </c>
       <c r="W31" s="14" t="inlineStr">
         <is>
           <t>HIGH</t>
@@ -4516,6 +4743,11 @@
       <c r="Y31" s="14" t="inlineStr">
         <is>
           <t>与EV/battery供应链、关键材料、出口管制或相关工业政策高度相关</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>snapshot</t>
         </is>
       </c>
     </row>
@@ -4625,6 +4857,11 @@
           <t>直接规定EV电池进入欧盟市场的合规与准入要求</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4732,6 +4969,11 @@
           <t>直接针对电池关键材料（锂/钴/镍/石墨）设定欧盟本土化与供应多元化基准</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4839,6 +5081,11 @@
           <t>直接决定中国EV产品进入欧盟市场的关税成本</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4946,6 +5193,11 @@
           <t>中国电池企业在欧盟设厂或并购面临东道国安全审查</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -5053,6 +5305,11 @@
           <t>直接决定中国EV/电池产品进入美国市场的关税成本</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -5160,6 +5417,11 @@
           <t>直接限制含中国电池组件的车辆获得美国市场补贴资格</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -5272,6 +5534,11 @@
           <t>一线整车企业原始披露：关税与出口管制对电池/整车供应链成本的影响</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5384,6 +5651,11 @@
           <t>一线整车企业原始披露：出口管制对车载半导体与零部件采购的直接约束</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -5491,6 +5763,11 @@
           <t>一线整车企业原始披露：出口管制对零部件/设备采购的直接约束</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -5598,6 +5875,11 @@
           <t>一线整车企业原始披露：2025 年中美关税升级对电芯外购供应链的影响</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -5710,6 +5992,11 @@
           <t>电池材料龙头原始披露：锂资源/加工布局与贸易政策风险</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -5827,6 +6114,11 @@
           <t>直接决定经墨西哥进入美国的电池/整车能否享受优惠关税</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -5939,6 +6231,11 @@
           <t>产业基线文件：需与印度最新电池/电动车产业政策配套解读</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -6051,6 +6348,11 @@
           <t>贸易数据：印度进口关税水平的官方量化基线</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -6163,6 +6465,11 @@
           <t>直接涉及镍与电池产业链的本地化/下游化要求</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6270,6 +6577,11 @@
           <t>供应链风险：产能转移后物流与通关效率的量化基准</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -6377,6 +6689,11 @@
           <t>直接约束锂/电池材料对美出口的强迫劳动合规要求</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -6484,6 +6801,11 @@
           <t>国际组织旗舰报告：EV/电池需求与制造贸易格局的系统性基线数据</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6594,6 +6916,11 @@
       <c r="Y50" t="inlineStr">
         <is>
           <t>行业量化数据：全球动力电池供给集中度与中国供应商份额</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>day</t>
         </is>
       </c>
     </row>
@@ -9563,7 +9890,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -10307,7 +10634,7 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -10369,7 +10696,7 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -10431,7 +10758,7 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>持续更新</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -10493,7 +10820,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>持续更新（每日）</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
@@ -10555,7 +10882,7 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>持续更新（每日）</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -11805,7 +12132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -11958,6 +12285,69 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>v0.9.1 P2 date/url cleanup</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>date：9 条非完整 ISO 中 6 条已改为具体日 —— CSIS_001=2026-08-04（PDF 原文 'Published August 4, 2026'）、TRD_001/002/003=2026-09-24、ITA_001/FR_001=2026-09-27（均为快照日）。</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>date：WTO_001 / IMF_001 / WTO_003 仍为月精度（原始文件只写 'March 2026' / 'April 2023' / 无日期），新增 date_precision 列标为 month，不臆造具体日。</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>sources 新增 date_precision（day|month|snapshot）与 shared_source_group 两列。</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>url：TRD_001/002/003 由同一个 Comtrade 首页改为各自可复跑的 TradeFlow 深链（含 reporter/partner/cmdCode/period 全参数）。</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>url：CASE_009 为时间线型案例（BIS_001+BIS_002 组成），来源改指联邦公报规则族检索页，不再与 BIS_002 共用同一篇公报链接。</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>url：CASE_004/005/006 确认为同一篇国盛证券研报，属真实同源而非重复录入，已用 shared_source_group=GS_OPTICAL_20251130 显式标注，三家公司年报原文仍列为待补。</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Task2_交付物/Task1/evidence_battery_EV_screened_v0.9.xlsx
+++ b/Task2_交付物/Task1/evidence_battery_EV_screened_v0.9.xlsx
@@ -1205,7 +1205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA50"/>
+  <dimension ref="A1:AA54"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="16.8"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="25"/>
@@ -6921,6 +6921,474 @@
       <c r="Z50" t="inlineStr">
         <is>
           <t>day</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>MOFCOM_003</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>对外投资合作国别（地区）指南：越南（2025年版）</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>官方报告</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻越南大使馆经济商务处</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>VN</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>CURRENT</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>https://www.mofcom.gov.cn/dl/gbdqzn/upload/yuenan.pdf</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>已核实</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>data/raw/policy/MOFCOM_003.pdf</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>越南政治环境总体稳定：官方指南称「越南是共产党领导的社会主义国家，政局稳定，政策连续性较好」，并把「政局稳定、经济发展较快、政策具有连续性」列为吸引外资主要优势之一。指南要求投资前「对项目所在地的政治风险和商业风险分析和规避」，并建议用中国信保覆盖国有化征收、汇兑限制、战争及政治暴乱等政治风险。</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>商务部《对外投资合作国别（地区）指南·越南（2025年版）》以「政局稳定、政策连续」为核心政治判断（1.4 政治环境、4.1 投资吸引力）；8.2 投资风险措施要求评估项目所在地政治风险，并用中国信保承保国有化征收、汇兑限制、战争及政治暴乱等政治风险。</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>指南为 2025 年版（前言签署于 2025 年 12 月）；商务部「国别（地区）指南」栏目按年覆盖同名 URL，本记录于 2026-10-16 抓取，内容标注为 2025 年版。政治环境为总体判断，具体项目仍需个案尽调。</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>东道国政治与投资环境的政府官方指引；为 EV/电池企业越南布局的政治风险提供权威依据</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>MOFCOM_004</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>对外投资合作国别（地区）指南：马来西亚（2025年版）</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>官方报告</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻马来西亚大使馆经济商务处</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>MY</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>CURRENT</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>https://www.mofcom.gov.cn/dl/gbdqzn/upload/malaixiya.pdf</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>已核实</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>data/raw/policy/MOFCOM_004.pdf</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>马来西亚政治风险总体较低但被单列为例（8.1 主要风险 (1) 政治风险）：存在「逐渐激烈的党派之争、美国对马来西亚的影响」等潜在政治风险，「政局总体平稳发展，但近年来政治斗争不断加剧」；跨国并购可能引发国家安全审查，战略性行业有股权限制，外资无法进入部分行业；国有化风险可由中国信保国家风险或多边投资担保机构承保。</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>《指南·马来西亚（2025年版）》8.1 主要风险：政治风险（党派之争加剧、外部（美国）影响）、环保风险、劳务引进风险、跨国并购的国家安全审查与战略性行业股权限制、国有化风险；8.2 要求事前评估政治与商业风险，并用政策性保险覆盖国有化等国家风险。</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>指南为 2025 年版（前言签署于 2025 年 12 月）；栏目按年覆盖同名 URL，本记录于 2026-10-16 抓取，内容标注为 2025 年版。</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>东道国政治与投资环境的政府官方指引；为 EV/电池企业马来西亚布局的政治与监管风险提供权威依据</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>MOFCOM_005</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>对外投资合作国别（地区）指南：印度（2025年版）</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>官方报告</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻印度大使馆经济商务处</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>CURRENT</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>https://www.mofcom.gov.cn/dl/gbdqzn/upload/yindu.pdf</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>已核实</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>data/raw/policy/MOFCOM_005.pdf</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>印度政局总体稳定、法律制度相对健全，但指南（8.1 主要风险）指出「印度虽积极吸引和利用外资，但对中国企业投资却存有戒心，通过多种政策手段严格限制中企对印新增投资」，营商环境「复杂性、不确定性和风险性」上升；2020 年以来印度海关、税务部门频繁对在印中资企业开展税务稽查、海关关税抽查、反洗钱调查，并严格限制中方员工工作签证新申与延签；8.2 要求「分析和规避项目所在地的政治风险和商业风险」并坚持依法合规经营。</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>《指南·印度（2025年版）》：政治环境称印度政局稳定、法律体系相对健全；8.1 主要风险指出印方对中资企业存有戒心并限制新增投资、营商环境不确定性与风险性上升（税务稽查、签证收紧）；8.2 要求评估政治与商业风险、依法合规经营（建议设专职合规审查）。</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>指南为 2025 年版（前言签署于 2025 年 12 月）；栏目按年覆盖同名 URL，本记录于 2026-10-16 抓取，内容标注为 2025 年版。中印投资限制随双边关系变动，需结合最新政策核实。</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>东道国政治与投资环境的政府官方指引；为 EV/电池企业印度布局的政治风险与合规风险提供权威依据</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>MOFCOM_006</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>对外投资合作国别（地区）指南：泰国（2025年版）</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>官方报告</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻泰国大使馆经济商务处</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>TH</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>CURRENT</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>https://www.mofcom.gov.cn/dl/gbdqzn/upload/taiguo.pdf</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>GENERAL</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>已核实</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>data/raw/policy/MOFCOM_006.pdf</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>泰国指南（8.1 主要风险）提示经济增速缓慢、承包工程市场竞争激烈、国际环境变化给投资企业带来压力；8.2.10/8.2.11 要求对「国有化征收、汇兑限制、战争及政治暴乱」等政治风险投保，并「与政府官员和各党派议员保持良好沟通，避免卷入政治纷争，重视重大项目潜在的政治风险」。</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>《指南·泰国（2025年版）》：8.1 主要风险列经济增速缓慢、承包工程高门槛竞争、国际环境变化压力；8.2 要求重视重大项目潜在政治风险、与政界保持沟通、避免卷入政治纷争，并用政策性保险覆盖国有化征收、汇兑限制、战争与政治暴乱等政治风险。</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>指南为 2025 年版（前言签署于 2025 年 12 月）；栏目按年覆盖同名 URL，本记录于 2026-10-16 抓取，内容标注为 2025 年版。泰国政局近年波动较大，本指南的政治判断偏总体性。</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>东道国政治与投资环境的政府官方指引；为 EV/电池企业泰国布局的政治风险提供权威依据</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>month</t>
         </is>
       </c>
     </row>
@@ -8988,7 +9456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L50"/>
+  <dimension ref="A1:L54"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -12101,6 +12569,254 @@
       <c r="L50" t="inlineStr">
         <is>
           <t>Supply Chain Risk; Operational Risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>MOFCOM_003</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>对外投资合作国别（地区）指南：越南（2025年版）</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>商务部对外投资和经济合作司、商务部国际贸易经济合作研究院</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>https://www.mofcom.gov.cn/dl/gbdqzn/upload/yuenan.pdf</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>EV_Battery</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Policy</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Political Risk; Regulatory Risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>MOFCOM_004</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>对外投资合作国别（地区）指南：马来西亚（2025年版）</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>商务部对外投资和经济合作司、商务部国际贸易经济合作研究院</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>https://www.mofcom.gov.cn/dl/gbdqzn/upload/malaixiya.pdf</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>EV_Battery</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Policy</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Political Risk; Regulatory Risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>MOFCOM_005</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>对外投资合作国别（地区）指南：印度（2025年版）</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>商务部对外投资和经济合作司、商务部国际贸易经济合作研究院</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>https://www.mofcom.gov.cn/dl/gbdqzn/upload/yindu.pdf</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>EV_Battery</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Policy</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Political Risk; Regulatory Risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>MOFCOM_006</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>对外投资合作国别（地区）指南：泰国（2025年版）</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>商务部对外投资和经济合作司、商务部国际贸易经济合作研究院</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>https://www.mofcom.gov.cn/dl/gbdqzn/upload/taiguo.pdf</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>EV_Battery</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Policy</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Political Risk; Regulatory Risk</t>
         </is>
       </c>
     </row>
@@ -12132,7 +12848,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -12170,7 +12886,7 @@
         </is>
       </c>
       <c r="B3" s="14" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" ht="17" customHeight="1">
@@ -12257,7 +12973,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>S 27 / A+ 12 / A 3 / B+ 6 / B 1（共 49）</t>
+          <t>S 31 / A+ 12 / A 3 / B+ 6 / B 1（共 53，v0.9.2 起）</t>
         </is>
       </c>
     </row>
@@ -12291,8 +13007,6 @@
           <t>v0.9.1 P2 date/url cleanup</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -12300,8 +13014,6 @@
           <t>date：9 条非完整 ISO 中 6 条已改为具体日 —— CSIS_001=2026-08-04（PDF 原文 'Published August 4, 2026'）、TRD_001/002/003=2026-09-24、ITA_001/FR_001=2026-09-27（均为快照日）。</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -12309,8 +13021,6 @@
           <t>date：WTO_001 / IMF_001 / WTO_003 仍为月精度（原始文件只写 'March 2026' / 'April 2023' / 无日期），新增 date_precision 列标为 month，不臆造具体日。</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -12318,8 +13028,6 @@
           <t>sources 新增 date_precision（day|month|snapshot）与 shared_source_group 两列。</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -12327,8 +13035,6 @@
           <t>url：TRD_001/002/003 由同一个 Comtrade 首页改为各自可复跑的 TradeFlow 深链（含 reporter/partner/cmdCode/period 全参数）。</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -12336,8 +13042,6 @@
           <t>url：CASE_009 为时间线型案例（BIS_001+BIS_002 组成），来源改指联邦公报规则族检索页，不再与 BIS_002 共用同一篇公报链接。</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -12345,8 +13049,49 @@
           <t>url：CASE_004/005/006 确认为同一篇国盛证券研报，属真实同源而非重复录入，已用 shared_source_group=GS_OPTICAL_20251130 显式标注，三家公司年报原文仍列为待补。</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>v0.9.2 Political Risk additions（东南亚＋印度）</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>新增 4 条</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>MOFCOM_003–006：商务部《对外投资合作国别（地区）指南》越南 / 马来西亚 / 印度 / 泰国（2025年版），来源类型=官方报告，authority=S，topic=对外投资（→ investment_policy；related_risk = Political Risk + Regulatory Risk），country=VN/MY/IN/TH；date=2025-12（date_precision=month，前言签署月）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>补齐的缺口</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Task 6 风险维度检索的 3 条 Political Risk missing（PLUS1_004 晶科能源、RETURN_002 富士康、RETURN_003 制造业外迁）此前在语料中无对应东道国政治风险材料；本批为语料侧补齐，不改检索词、不改产品代码。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>uncertainty / 可复现性</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>商务部国别指南栏目按年覆盖同名 URL（无版本号）；4 个 PDF 于 2026-10-16 抓取、内容标注为 2025 年版，raw 文件已入库。URL 需带 Referer=https://fec.mofcom.gov.cn/channel/gbdqzn.shtml 才可下载。</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
